--- a/app/webapp/MaintenanceOrders_Template.xlsx
+++ b/app/webapp/MaintenanceOrders_Template.xlsx
@@ -1,55 +1,426 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="MaintenanceOrders" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="MaintenanceOrders" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Operations" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Materials" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="MasterData_Reference" state="visible" r:id="rId7"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="120">
+  <si>
+    <t>Order</t>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Plant</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Planner</t>
+  </si>
+  <si>
+    <t>ScheduledFrom</t>
+  </si>
+  <si>
+    <t>ScheduledTo</t>
+  </si>
+  <si>
+    <t>Operations (Inline Optional)</t>
+  </si>
+  <si>
+    <t>Materials (Inline Optional)</t>
+  </si>
+  <si>
+    <t>MO-2001</t>
+  </si>
+  <si>
+    <t>EQ-001</t>
+  </si>
+  <si>
+    <t>Pump A Monthly Overhaul &amp; Inspection</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>PREVENTIVE</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>JOHN</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>MO-2002</t>
+  </si>
+  <si>
+    <t>EQ-002</t>
+  </si>
+  <si>
+    <t>Motor Bearing Check &amp; Alignment</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>CORRECTIVE</t>
+  </si>
+  <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
+    <t>SARAH</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>MO-2003</t>
+  </si>
+  <si>
+    <t>EQ-003</t>
+  </si>
+  <si>
+    <t>Emergency Valve Fix &amp; Replacement</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>EMERGENCY</t>
+  </si>
+  <si>
+    <t>CRITICAL</t>
+  </si>
+  <si>
+    <t>ALEX</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>MO-2004</t>
+  </si>
+  <si>
+    <t>EQ-004</t>
+  </si>
+  <si>
+    <t>Conveyor Belt Tension Tuning</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>2026-09-20</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>10:Tension Check:2; 20:Alignment:1</t>
+  </si>
+  <si>
+    <t>MAT-005:10</t>
+  </si>
+  <si>
+    <t>MO-2005</t>
+  </si>
+  <si>
+    <t>EQ-005</t>
+  </si>
+  <si>
+    <t>Turbine Lubricant &amp; Filter Service</t>
+  </si>
+  <si>
+    <t>2026-09-22</t>
+  </si>
+  <si>
+    <t>10:Drain Oil:1; 20:Refill Lubricant:2</t>
+  </si>
+  <si>
+    <t>MAT-003:5; MAT-002:1</t>
+  </si>
+  <si>
+    <t>OperationNo</t>
+  </si>
+  <si>
+    <t>WorkCenter</t>
+  </si>
+  <si>
+    <t>Technician</t>
+  </si>
+  <si>
+    <t>PlannedHours</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Visual pump inspection &amp; vibration test</t>
+  </si>
+  <si>
+    <t>WC-001</t>
+  </si>
+  <si>
+    <t>T-001</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Dismantle housing and check seals</t>
+  </si>
+  <si>
+    <t>WC-002</t>
+  </si>
+  <si>
+    <t>T-002</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Reassemble and conduct pressure test</t>
+  </si>
+  <si>
+    <t>WC-003</t>
+  </si>
+  <si>
+    <t>T-003</t>
+  </si>
+  <si>
+    <t>Measure motor bearing temperature</t>
+  </si>
+  <si>
+    <t>Grease motor bearings</t>
+  </si>
+  <si>
+    <t>Shut down pipeline &amp; isolate valve</t>
+  </si>
+  <si>
+    <t>Replace broken valve core and seals</t>
+  </si>
+  <si>
+    <t>Material</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>MAT-001</t>
+  </si>
+  <si>
+    <t>EA</t>
+  </si>
+  <si>
+    <t>MAT-003</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>MAT-002</t>
+  </si>
+  <si>
+    <t>MAT-005</t>
+  </si>
+  <si>
+    <t>SET</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Code / Key</t>
+  </si>
+  <si>
+    <t>Description / Details</t>
+  </si>
+  <si>
+    <t>Unit Price (USD)</t>
+  </si>
+  <si>
+    <t>Centrifugal Pump A1 (Plant 1000)</t>
+  </si>
+  <si>
+    <t>Hydraulic Motor B2 (Plant 2000)</t>
+  </si>
+  <si>
+    <t>Safety Valve C3 (Plant 3000)</t>
+  </si>
+  <si>
+    <t>Belt Conveyor D4 (Plant 1000)</t>
+  </si>
+  <si>
+    <t>Gas Turbine E5 (Plant 2000)</t>
+  </si>
+  <si>
+    <t>Main Production Plant</t>
+  </si>
+  <si>
+    <t>Chemical Processing Plant</t>
+  </si>
+  <si>
+    <t>Assembly &amp; Packaging Plant</t>
+  </si>
+  <si>
+    <t>Maintenance Type</t>
+  </si>
+  <si>
+    <t>Planned preventive maintenance</t>
+  </si>
+  <si>
+    <t>Corrective maintenance after fault</t>
+  </si>
+  <si>
+    <t>Immediate emergency breakdown fix</t>
+  </si>
+  <si>
+    <t>Low priority (normal SLA)</t>
+  </si>
+  <si>
+    <t>Medium standard priority</t>
+  </si>
+  <si>
+    <t>High priority maintenance</t>
+  </si>
+  <si>
+    <t>Critical (Same-day schedule mandatory)</t>
+  </si>
+  <si>
+    <t>John Doe (Mechanical Lead)</t>
+  </si>
+  <si>
+    <t>Sarah Connor (Automation Lead)</t>
+  </si>
+  <si>
+    <t>Alex Smith (Electrical Lead)</t>
+  </si>
+  <si>
+    <t>Work Center</t>
+  </si>
+  <si>
+    <t>Mechanical Workshop 1</t>
+  </si>
+  <si>
+    <t>Electrical Workshop 2</t>
+  </si>
+  <si>
+    <t>Hydraulics Workshop 3</t>
+  </si>
+  <si>
+    <t>Material Master</t>
+  </si>
+  <si>
+    <t>Heavy Duty Ball Bearing (EA)</t>
+  </si>
+  <si>
+    <t>25.00</t>
+  </si>
+  <si>
+    <t>High Pressure Seal Kit (EA)</t>
+  </si>
+  <si>
+    <t>40.00</t>
+  </si>
+  <si>
+    <t>Synthetic Industrial Lubricant (L)</t>
+  </si>
+  <si>
+    <t>MAT-004</t>
+  </si>
+  <si>
+    <t>Flexible Motor Coupling (EA)</t>
+  </si>
+  <si>
+    <t>150.00</t>
+  </si>
+  <si>
+    <t>Stainless Steel Bolts &amp; Nuts (SET)</t>
+  </si>
+  <si>
+    <t>10.00</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF004B87"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF007079"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF107E3E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A5568"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -64,14 +435,43 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,186 +796,918 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="36" customWidth="1"/>
+    <col min="11" max="11" width="34" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Order</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Equipment</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Description</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Plant</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Type</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Priority</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Planner</v>
-      </c>
-      <c r="H1" t="str">
-        <v>ScheduledFrom</v>
-      </c>
-      <c r="I1" t="str">
-        <v>ScheduledTo</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>MO-2001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>EQ-001</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Pump A Monthly Inspection</v>
-      </c>
-      <c r="D2" t="str">
-        <v>1000</v>
-      </c>
-      <c r="E2" t="str">
-        <v>PREVENTIVE</v>
-      </c>
-      <c r="F2" t="str">
-        <v>HIGH</v>
-      </c>
-      <c r="G2" t="str">
-        <v>John Doe</v>
-      </c>
-      <c r="H2" t="str">
-        <v>2026-09-10</v>
-      </c>
-      <c r="I2" t="str">
-        <v>2026-09-15</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>MO-2002</v>
-      </c>
-      <c r="B3" t="str">
-        <v>EQ-002</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Motor Bearing Check</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2000</v>
-      </c>
-      <c r="E3" t="str">
-        <v>CORRECTIVE</v>
-      </c>
-      <c r="F3" t="str">
-        <v>MEDIUM</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Sarah Connor</v>
-      </c>
-      <c r="H3" t="str">
-        <v>2026-09-12</v>
-      </c>
-      <c r="I3" t="str">
-        <v>2026-09-18</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>MO-2003</v>
-      </c>
-      <c r="B4" t="str">
-        <v>EQ-003</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Emergency Valve Fix</v>
-      </c>
-      <c r="D4" t="str">
-        <v>3000</v>
-      </c>
-      <c r="E4" t="str">
-        <v>EMERGENCY</v>
-      </c>
-      <c r="F4" t="str">
-        <v>CRITICAL</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Alex Smith</v>
-      </c>
-      <c r="H4" t="str">
-        <v>2026-09-05</v>
-      </c>
-      <c r="I4" t="str">
-        <v>2026-09-05</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>MO-2004</v>
-      </c>
-      <c r="B5" t="str">
-        <v>EQ-004</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Conveyor Belt Alignment</v>
-      </c>
-      <c r="D5" t="str">
-        <v>1000</v>
-      </c>
-      <c r="E5" t="str">
-        <v>PREVENTIVE</v>
-      </c>
-      <c r="F5" t="str">
-        <v>LOW</v>
-      </c>
-      <c r="G5" t="str">
-        <v>John Doe</v>
-      </c>
-      <c r="H5" t="str">
-        <v>2026-09-20</v>
-      </c>
-      <c r="I5" t="str">
-        <v>2026-09-25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>MO-2005</v>
-      </c>
-      <c r="B6" t="str">
-        <v>EQ-005</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Turbine Oil Replacement</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2000</v>
-      </c>
-      <c r="E6" t="str">
-        <v>PREVENTIVE</v>
-      </c>
-      <c r="F6" t="str">
-        <v>HIGH</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Sarah Connor</v>
-      </c>
-      <c r="H6" t="str">
-        <v>2026-09-15</v>
-      </c>
-      <c r="I6" t="str">
-        <v>2026-09-22</v>
+    <row r="1" ht="26" customHeight="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I6"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="4" max="6" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="5">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="5">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="5">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="5">
+        <v>5</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" s="5">
+        <v>8</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/app/webapp/MaintenanceOrders_Template.xlsx
+++ b/app/webapp/MaintenanceOrders_Template.xlsx
@@ -14,10 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="120">
-  <si>
-    <t>Order</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="120">
   <si>
     <t>Equipment</t>
   </si>
@@ -49,9 +46,6 @@
     <t>Materials (Inline Optional)</t>
   </si>
   <si>
-    <t>MO-2001</t>
-  </si>
-  <si>
     <t>EQ-001</t>
   </si>
   <si>
@@ -76,205 +70,211 @@
     <t>2026-09-15</t>
   </si>
   <si>
+    <t>10:Visual pump inspection:2; 20:Dismantle housing:3.5; 30:Reassemble &amp; test:2</t>
+  </si>
+  <si>
+    <t>MAT-001:2; MAT-003:5</t>
+  </si>
+  <si>
+    <t>EQ-002</t>
+  </si>
+  <si>
+    <t>Motor Bearing Check &amp; Alignment</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>CORRECTIVE</t>
+  </si>
+  <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
+    <t>SARAH</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>10:Measure bearing temp:1.5; 20:Grease motor bearings:1</t>
+  </si>
+  <si>
+    <t>MAT-001:1; MAT-003:2</t>
+  </si>
+  <si>
+    <t>EQ-003</t>
+  </si>
+  <si>
+    <t>Emergency Valve Fix &amp; Replacement</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>EMERGENCY</t>
+  </si>
+  <si>
+    <t>CRITICAL</t>
+  </si>
+  <si>
+    <t>ALEX</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>10:Isolate valve:1; 20:Replace valve core &amp; seals:4</t>
+  </si>
+  <si>
+    <t>MAT-002:1; MAT-005:8</t>
+  </si>
+  <si>
+    <t>EQ-004</t>
+  </si>
+  <si>
+    <t>Conveyor Belt Tension Tuning</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>2026-09-20</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>10:Tension Check:2; 20:Alignment:1</t>
+  </si>
+  <si>
+    <t>MAT-005:10</t>
+  </si>
+  <si>
+    <t>EQ-005</t>
+  </si>
+  <si>
+    <t>Turbine Lubricant &amp; Filter Service</t>
+  </si>
+  <si>
+    <t>2026-09-22</t>
+  </si>
+  <si>
+    <t>10:Drain Oil:1; 20:Refill Lubricant:2</t>
+  </si>
+  <si>
+    <t>MAT-003:5; MAT-002:1</t>
+  </si>
+  <si>
+    <t>OperationNo</t>
+  </si>
+  <si>
+    <t>WorkCenter</t>
+  </si>
+  <si>
+    <t>Technician</t>
+  </si>
+  <si>
+    <t>PlannedHours</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Visual pump inspection &amp; vibration test</t>
+  </si>
+  <si>
+    <t>WC-001</t>
+  </si>
+  <si>
+    <t>T-001</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Dismantle housing and check seals</t>
+  </si>
+  <si>
+    <t>WC-002</t>
+  </si>
+  <si>
+    <t>T-002</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Reassemble and conduct pressure test</t>
+  </si>
+  <si>
+    <t>WC-003</t>
+  </si>
+  <si>
+    <t>T-003</t>
+  </si>
+  <si>
+    <t>Measure motor bearing temperature</t>
+  </si>
+  <si>
+    <t>Grease motor bearings</t>
+  </si>
+  <si>
+    <t>Shut down pipeline &amp; isolate valve</t>
+  </si>
+  <si>
+    <t>Replace broken valve core and seals</t>
+  </si>
+  <si>
+    <t>Material</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>MAT-001</t>
+  </si>
+  <si>
+    <t>EA</t>
+  </si>
+  <si>
+    <t>MAT-003</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>MAT-002</t>
+  </si>
+  <si>
+    <t>MAT-005</t>
+  </si>
+  <si>
+    <t>SET</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Code / Key</t>
+  </si>
+  <si>
+    <t>Description / Details</t>
+  </si>
+  <si>
+    <t>Unit Price (USD)</t>
+  </si>
+  <si>
+    <t>Centrifugal Pump A1 (Plant 1000)</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t>MO-2002</t>
-  </si>
-  <si>
-    <t>EQ-002</t>
-  </si>
-  <si>
-    <t>Motor Bearing Check &amp; Alignment</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>CORRECTIVE</t>
-  </si>
-  <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
-    <t>SARAH</t>
-  </si>
-  <si>
-    <t>2026-09-12</t>
-  </si>
-  <si>
-    <t>2026-09-18</t>
-  </si>
-  <si>
-    <t>MO-2003</t>
-  </si>
-  <si>
-    <t>EQ-003</t>
-  </si>
-  <si>
-    <t>Emergency Valve Fix &amp; Replacement</t>
-  </si>
-  <si>
-    <t>3000</t>
-  </si>
-  <si>
-    <t>EMERGENCY</t>
-  </si>
-  <si>
-    <t>CRITICAL</t>
-  </si>
-  <si>
-    <t>ALEX</t>
-  </si>
-  <si>
-    <t>2026-09-05</t>
-  </si>
-  <si>
-    <t>MO-2004</t>
-  </si>
-  <si>
-    <t>EQ-004</t>
-  </si>
-  <si>
-    <t>Conveyor Belt Tension Tuning</t>
-  </si>
-  <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>2026-09-20</t>
-  </si>
-  <si>
-    <t>2026-09-25</t>
-  </si>
-  <si>
-    <t>10:Tension Check:2; 20:Alignment:1</t>
-  </si>
-  <si>
-    <t>MAT-005:10</t>
-  </si>
-  <si>
-    <t>MO-2005</t>
-  </si>
-  <si>
-    <t>EQ-005</t>
-  </si>
-  <si>
-    <t>Turbine Lubricant &amp; Filter Service</t>
-  </si>
-  <si>
-    <t>2026-09-22</t>
-  </si>
-  <si>
-    <t>10:Drain Oil:1; 20:Refill Lubricant:2</t>
-  </si>
-  <si>
-    <t>MAT-003:5; MAT-002:1</t>
-  </si>
-  <si>
-    <t>OperationNo</t>
-  </si>
-  <si>
-    <t>WorkCenter</t>
-  </si>
-  <si>
-    <t>Technician</t>
-  </si>
-  <si>
-    <t>PlannedHours</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Visual pump inspection &amp; vibration test</t>
-  </si>
-  <si>
-    <t>WC-001</t>
-  </si>
-  <si>
-    <t>T-001</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>Dismantle housing and check seals</t>
-  </si>
-  <si>
-    <t>WC-002</t>
-  </si>
-  <si>
-    <t>T-002</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>Reassemble and conduct pressure test</t>
-  </si>
-  <si>
-    <t>WC-003</t>
-  </si>
-  <si>
-    <t>T-003</t>
-  </si>
-  <si>
-    <t>Measure motor bearing temperature</t>
-  </si>
-  <si>
-    <t>Grease motor bearings</t>
-  </si>
-  <si>
-    <t>Shut down pipeline &amp; isolate valve</t>
-  </si>
-  <si>
-    <t>Replace broken valve core and seals</t>
-  </si>
-  <si>
-    <t>Material</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>MAT-001</t>
-  </si>
-  <si>
-    <t>EA</t>
-  </si>
-  <si>
-    <t>MAT-003</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>MAT-002</t>
-  </si>
-  <si>
-    <t>MAT-005</t>
-  </si>
-  <si>
-    <t>SET</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Code / Key</t>
-  </si>
-  <si>
-    <t>Description / Details</t>
-  </si>
-  <si>
-    <t>Unit Price (USD)</t>
-  </si>
-  <si>
-    <t>Centrifugal Pump A1 (Plant 1000)</t>
   </si>
   <si>
     <t>Hydraulic Motor B2 (Plant 2000)</t>
@@ -797,20 +797,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="36" customWidth="1"/>
-    <col min="11" max="11" width="34" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="36" customWidth="1"/>
+    <col min="10" max="10" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="26" customHeight="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -841,88 +841,79 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="2" t="s">
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -938,86 +929,77 @@
         <v>36</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="C5" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="D5" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="3" t="s">
         <v>43</v>
       </c>
+      <c r="I5" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="J5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K5" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="20" customHeight="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="2" t="s">
         <v>49</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1041,36 +1023,36 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="F2" s="5">
         <v>2</v>
@@ -1078,19 +1060,19 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="F3" s="5">
         <v>3.5</v>
@@ -1098,19 +1080,19 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="F4" s="5">
         <v>2</v>
@@ -1118,19 +1100,19 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="F5" s="5">
         <v>1.5</v>
@@ -1138,19 +1120,19 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="F6" s="5">
         <v>1</v>
@@ -1161,16 +1143,16 @@
         <v>30</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="F7" s="5">
         <v>1</v>
@@ -1181,16 +1163,16 @@
         <v>30</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="F8" s="5">
         <v>4</v>
@@ -1218,69 +1200,69 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C2" s="5">
         <v>2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" s="5">
         <v>5</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C4" s="5">
         <v>1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C5" s="5">
         <v>2</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1288,13 +1270,13 @@
         <v>30</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C6" s="5">
         <v>1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1302,13 +1284,13 @@
         <v>30</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C7" s="5">
         <v>8</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1330,63 +1312,63 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>87</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>39</v>
@@ -1395,63 +1377,63 @@
         <v>89</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>90</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>93</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1459,13 +1441,13 @@
         <v>94</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1473,13 +1455,13 @@
         <v>94</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>96</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1487,18 +1469,18 @@
         <v>94</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>97</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>41</v>
@@ -1507,91 +1489,91 @@
         <v>98</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>99</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>100</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>101</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>103</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>104</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1599,13 +1581,13 @@
         <v>105</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>106</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1613,13 +1595,13 @@
         <v>105</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>107</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1627,13 +1609,13 @@
         <v>105</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>108</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1641,7 +1623,7 @@
         <v>109</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>110</v>
@@ -1655,7 +1637,7 @@
         <v>109</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>112</v>
@@ -1669,7 +1651,7 @@
         <v>109</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>114</v>
@@ -1697,7 +1679,7 @@
         <v>109</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>118</v>
